--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto.xlsx
@@ -2799,7 +2799,7 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>1.571654911485923</v>
+        <v>1.571654911485924</v>
       </c>
       <c r="C144">
         <v>1.547263449305733</v>
@@ -7409,7 +7409,7 @@
         <v>0.7099315591087915</v>
       </c>
       <c r="C415">
-        <v>0.6895296474122918</v>
+        <v>0.6895296474122917</v>
       </c>
       <c r="D415">
         <v>0.9339360583890401</v>
@@ -7508,7 +7508,7 @@
         <v>420</v>
       </c>
       <c r="B421">
-        <v>0.7169244950076398</v>
+        <v>0.7169244950076397</v>
       </c>
       <c r="C421">
         <v>0.6811198886750538</v>
@@ -7576,7 +7576,7 @@
         <v>424</v>
       </c>
       <c r="B425">
-        <v>0.7244435389589284</v>
+        <v>0.7244435389589283</v>
       </c>
       <c r="C425">
         <v>0.8075483342687538</v>
